--- a/InfoChartUpdated.xlsx
+++ b/InfoChartUpdated.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="245">
   <si>
     <t>Relic cost</t>
   </si>
@@ -270,7 +270,7 @@
 Mandatory buffer for higher odyssey/heart spire.</t>
   </si>
   <si>
-    <t xml:space="preserve">TBA
+    <t xml:space="preserve">B
 </t>
   </si>
   <si>
@@ -571,6 +571,23 @@
 Requires to properly connect sun and moon targets.</t>
   </si>
   <si>
+    <t xml:space="preserve">Serket
+</t>
+  </si>
+  <si>
+    <t>Early 10-20
+Late 30</t>
+  </si>
+  <si>
+    <t>Backline access. Does no damage on its own but can stall regardless of deficit
+for some of the longest periods of all frontliners we have in the game.
+Recommended to build for PvP/Later odyssey as frontliner.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A~S
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">Hercules
 </t>
   </si>
@@ -599,10 +616,6 @@
   <si>
     <t>Recommended frontline unit , can be a solo carry up until 5 teams.
 Need to get some dodge% on slot 2/3.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B
-</t>
   </si>
   <si>
     <t>Phoenix</t>
@@ -2582,19 +2595,19 @@
         <v>152</v>
       </c>
       <c r="E3" s="30" t="s">
+        <v>73</v>
+      </c>
+      <c r="F3" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="F3" s="30" t="s">
-        <v>73</v>
-      </c>
       <c r="G3" s="30" t="s">
-        <v>45</v>
+        <v>153</v>
       </c>
       <c r="H3" s="30" t="s">
         <v>46</v>
       </c>
       <c r="I3" s="30" t="s">
-        <v>153</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4">
@@ -2611,155 +2624,155 @@
         <v>156</v>
       </c>
       <c r="E4" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="F4" s="30" t="s">
         <v>73</v>
-      </c>
-      <c r="F4" s="30" t="s">
-        <v>157</v>
       </c>
       <c r="G4" s="30" t="s">
         <v>45</v>
       </c>
       <c r="H4" s="30" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="I4" s="30" t="s">
-        <v>47</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="30" t="s">
         <v>158</v>
       </c>
-      <c r="B5" s="30">
-        <v>20.0</v>
+      <c r="B5" s="30" t="s">
+        <v>159</v>
       </c>
       <c r="C5" s="30" t="s">
-        <v>109</v>
+        <v>60</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E5" s="30" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="F5" s="30" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="G5" s="30" t="s">
-        <v>89</v>
+        <v>45</v>
       </c>
       <c r="H5" s="30" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="I5" s="30" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="30" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B6" s="30">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="C6" s="30" t="s">
         <v>109</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E6" s="30" t="s">
         <v>89</v>
       </c>
       <c r="F6" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="G6" s="30" t="s">
         <v>89</v>
-      </c>
-      <c r="G6" s="30" t="s">
-        <v>81</v>
       </c>
       <c r="H6" s="30" t="s">
         <v>83</v>
       </c>
       <c r="I6" s="30" t="s">
-        <v>162</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="30" t="s">
         <v>163</v>
       </c>
-      <c r="B7" s="30" t="s">
+      <c r="B7" s="30">
+        <v>10.0</v>
+      </c>
+      <c r="C7" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="D7" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="C7" s="30" t="s">
+      <c r="E7" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="F7" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="G7" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="H7" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="I7" s="30" t="s">
         <v>165</v>
-      </c>
-      <c r="D7" s="30" t="s">
-        <v>166</v>
-      </c>
-      <c r="E7" s="30" t="s">
-        <v>73</v>
-      </c>
-      <c r="F7" s="30" t="s">
-        <v>73</v>
-      </c>
-      <c r="G7" s="30" t="s">
-        <v>157</v>
-      </c>
-      <c r="H7" s="30" t="s">
-        <v>167</v>
-      </c>
-      <c r="I7" s="30" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="B8" s="30" t="s">
+        <v>167</v>
+      </c>
+      <c r="C8" s="30" t="s">
         <v>168</v>
       </c>
-      <c r="B8" s="30">
-        <v>0.0</v>
-      </c>
-      <c r="C8" s="30" t="s">
+      <c r="D8" s="30" t="s">
         <v>169</v>
       </c>
-      <c r="D8" s="30" t="s">
+      <c r="E8" s="30" t="s">
+        <v>73</v>
+      </c>
+      <c r="F8" s="30" t="s">
+        <v>73</v>
+      </c>
+      <c r="G8" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="H8" s="30" t="s">
         <v>170</v>
       </c>
-      <c r="E8" s="30" t="s">
-        <v>88</v>
-      </c>
-      <c r="F8" s="30" t="s">
-        <v>88</v>
-      </c>
-      <c r="G8" s="30" t="s">
-        <v>98</v>
-      </c>
-      <c r="H8" s="30" t="s">
-        <v>103</v>
-      </c>
       <c r="I8" s="30" t="s">
-        <v>171</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="30" t="s">
+        <v>171</v>
+      </c>
+      <c r="B9" s="30">
+        <v>0.0</v>
+      </c>
+      <c r="C9" s="30" t="s">
         <v>172</v>
       </c>
-      <c r="B9" s="30" t="s">
+      <c r="D9" s="30" t="s">
         <v>173</v>
-      </c>
-      <c r="C9" s="30" t="s">
-        <v>174</v>
-      </c>
-      <c r="D9" s="30" t="s">
-        <v>175</v>
       </c>
       <c r="E9" s="30" t="s">
         <v>88</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="G9" s="30" t="s">
         <v>98</v>
@@ -2768,65 +2781,94 @@
         <v>103</v>
       </c>
       <c r="I9" s="30" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="30" t="s">
+        <v>175</v>
+      </c>
+      <c r="B10" s="30" t="s">
         <v>176</v>
       </c>
-      <c r="B10" s="30" t="s">
+      <c r="C10" s="30" t="s">
         <v>177</v>
       </c>
-      <c r="C10" s="30" t="s">
+      <c r="D10" s="30" t="s">
         <v>178</v>
       </c>
-      <c r="D10" s="30" t="s">
-        <v>179</v>
-      </c>
       <c r="E10" s="30" t="s">
-        <v>180</v>
+        <v>88</v>
       </c>
       <c r="F10" s="30" t="s">
-        <v>157</v>
+        <v>98</v>
       </c>
       <c r="G10" s="30" t="s">
-        <v>157</v>
+        <v>98</v>
       </c>
       <c r="H10" s="30" t="s">
-        <v>181</v>
+        <v>103</v>
       </c>
       <c r="I10" s="30" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="30" t="s">
+        <v>179</v>
+      </c>
+      <c r="B11" s="30" t="s">
+        <v>180</v>
+      </c>
+      <c r="C11" s="30" t="s">
+        <v>181</v>
+      </c>
+      <c r="D11" s="30" t="s">
+        <v>182</v>
+      </c>
+      <c r="E11" s="30" t="s">
         <v>183</v>
       </c>
-      <c r="B11" s="30">
+      <c r="F11" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="G11" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="H11" s="30" t="s">
+        <v>184</v>
+      </c>
+      <c r="I11" s="30" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="B12" s="30">
         <v>0.0</v>
       </c>
-      <c r="C11" s="30" t="s">
+      <c r="C12" s="30" t="s">
         <v>139</v>
       </c>
-      <c r="D11" s="30" t="s">
-        <v>184</v>
-      </c>
-      <c r="E11" s="30" t="s">
+      <c r="D12" s="30" t="s">
+        <v>187</v>
+      </c>
+      <c r="E12" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="F11" s="30" t="s">
+      <c r="F12" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="G11" s="30" t="s">
+      <c r="G12" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="H11" s="30" t="s">
+      <c r="H12" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="I11" s="30" t="s">
-        <v>171</v>
+      <c r="I12" s="30" t="s">
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -2879,16 +2921,16 @@
     </row>
     <row r="2">
       <c r="A2" s="32" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B2" s="32" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C2" s="32" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D2" s="32" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E2" s="32" t="s">
         <v>45</v>
@@ -2903,21 +2945,21 @@
         <v>46</v>
       </c>
       <c r="I2" s="32" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="32" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B3" s="32" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C3" s="32" t="s">
         <v>60</v>
       </c>
       <c r="D3" s="32" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="E3" s="32" t="s">
         <v>45</v>
@@ -2932,50 +2974,50 @@
         <v>46</v>
       </c>
       <c r="I3" s="32" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="32" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B4" s="32" t="s">
         <v>64</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E4" s="32" t="s">
         <v>45</v>
       </c>
       <c r="F4" s="32" t="s">
-        <v>157</v>
+        <v>67</v>
       </c>
       <c r="G4" s="32" t="s">
-        <v>157</v>
+        <v>67</v>
       </c>
       <c r="H4" s="32" t="s">
         <v>68</v>
       </c>
       <c r="I4" s="32" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="32" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C5" s="32" t="s">
         <v>101</v>
       </c>
       <c r="D5" s="32" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E5" s="32" t="s">
         <v>89</v>
@@ -2995,16 +3037,16 @@
     </row>
     <row r="6">
       <c r="A6" s="32" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C6" s="32" t="s">
         <v>60</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E6" s="32" t="s">
         <v>73</v>
@@ -3024,16 +3066,16 @@
     </row>
     <row r="7">
       <c r="A7" s="32" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B7" s="32" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C7" s="32" t="s">
         <v>60</v>
       </c>
       <c r="D7" s="32" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="E7" s="32" t="s">
         <v>45</v>
@@ -3053,7 +3095,7 @@
     </row>
     <row r="8">
       <c r="A8" s="32" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B8" s="32">
         <v>1.0</v>
@@ -3062,7 +3104,7 @@
         <v>109</v>
       </c>
       <c r="D8" s="32" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="E8" s="32" t="s">
         <v>89</v>
@@ -3077,50 +3119,50 @@
         <v>83</v>
       </c>
       <c r="I8" s="32" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="32" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B9" s="32" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D9" s="32" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="F9" s="32" t="s">
         <v>73</v>
       </c>
       <c r="G9" s="32" t="s">
-        <v>157</v>
+        <v>67</v>
       </c>
       <c r="H9" s="32" t="s">
         <v>75</v>
       </c>
       <c r="I9" s="32" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="32" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B10" s="32">
         <v>0.0</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D10" s="32" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E10" s="32" t="s">
         <v>88</v>
@@ -3135,12 +3177,12 @@
         <v>103</v>
       </c>
       <c r="I10" s="32" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="32" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B11" s="32">
         <v>0.0</v>
@@ -3149,7 +3191,7 @@
         <v>139</v>
       </c>
       <c r="D11" s="32" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E11" s="32" t="s">
         <v>88</v>
@@ -3164,7 +3206,7 @@
         <v>103</v>
       </c>
       <c r="I11" s="32" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
   </sheetData>
@@ -3220,16 +3262,16 @@
     </row>
     <row r="2">
       <c r="A2" s="35" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B2" s="35" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C2" s="35" t="s">
         <v>50</v>
       </c>
       <c r="D2" s="35" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E2" s="35" t="s">
         <v>52</v>
@@ -3249,16 +3291,16 @@
     </row>
     <row r="3">
       <c r="A3" s="35" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C3" s="35" t="s">
         <v>50</v>
       </c>
       <c r="D3" s="35" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E3" s="35" t="s">
         <v>52</v>
@@ -3278,7 +3320,7 @@
     </row>
     <row r="4">
       <c r="A4" s="35" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B4" s="35">
         <v>30.0</v>
@@ -3287,7 +3329,7 @@
         <v>50</v>
       </c>
       <c r="D4" s="35" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E4" s="35" t="s">
         <v>52</v>
@@ -3302,21 +3344,21 @@
         <v>53</v>
       </c>
       <c r="I4" s="35" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="35" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B5" s="35">
         <v>30.0</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D5" s="35" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E5" s="35" t="s">
         <v>52</v>
@@ -3331,12 +3373,12 @@
         <v>53</v>
       </c>
       <c r="I5" s="35" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B6" s="35">
         <v>30.0</v>
@@ -3345,7 +3387,7 @@
         <v>50</v>
       </c>
       <c r="D6" s="35" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E6" s="35" t="s">
         <v>52</v>
@@ -3360,12 +3402,12 @@
         <v>83</v>
       </c>
       <c r="I6" s="35" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B7" s="35">
         <v>30.0</v>
@@ -3374,10 +3416,10 @@
         <v>50</v>
       </c>
       <c r="D7" s="35" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="E7" s="35" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="F7" s="35" t="s">
         <v>52</v>
@@ -3389,21 +3431,21 @@
         <v>83</v>
       </c>
       <c r="I7" s="35" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B8" s="35" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D8" s="35" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="E8" s="35" t="s">
         <v>89</v>
@@ -3418,7 +3460,7 @@
         <v>83</v>
       </c>
       <c r="I8" s="35" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>

--- a/InfoChartUpdated.xlsx
+++ b/InfoChartUpdated.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="250">
   <si>
     <t>Relic cost</t>
   </si>
@@ -372,10 +372,6 @@
     <t>Isis</t>
   </si>
   <si>
-    <t>0
-30 (Late)</t>
-  </si>
-  <si>
     <t>Heart spire 
 Boss</t>
   </si>
@@ -386,6 +382,9 @@
     <t>C</t>
   </si>
   <si>
+    <t>T10</t>
+  </si>
+  <si>
     <t>Can rush divine for 5 lvl 300 early game.</t>
   </si>
   <si>
@@ -399,9 +398,6 @@
     <t>Protection unit for PvP carry such as nezha.</t>
   </si>
   <si>
-    <t>T10</t>
-  </si>
-  <si>
     <t>Get divine after everyone above is divine.</t>
   </si>
   <si>
@@ -441,6 +437,19 @@
   <si>
     <t xml:space="preserve">Divine-D5
 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eris
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Odyssey
+</t>
+  </si>
+  <si>
+    <t>Purely a odyssey carry. Does not do much in pvp and wont be the unit that will single handedly
+progress your club spire. Her damage once she gets r30 is insane. Give her teammates to buy time for 
+her puppets to not die. If puppets die u will deal 0 dmg. (Will get her bis team in 2~ months)</t>
   </si>
   <si>
     <t xml:space="preserve">Anubis
@@ -765,10 +774,6 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Odyssey
-</t>
-  </si>
-  <si>
     <t>Only carry aside jingwei that can be used up till late game from standard units.
 Forms a core with yuelao+momus.
 Doesn't contest teammates with other carries.</t>
@@ -880,6 +885,18 @@
   </si>
   <si>
     <t>Base dupe, work on dupes after zeus/nezha</t>
+  </si>
+  <si>
+    <t>Hera</t>
+  </si>
+  <si>
+    <t>Odyssey / PvP / Spire</t>
+  </si>
+  <si>
+    <t>Higher the deficit more value she has as a unit. Can near solo wipe teams via her charm mechanic.</t>
+  </si>
+  <si>
+    <t>Base dupe</t>
   </si>
   <si>
     <t>Amun</t>
@@ -2054,26 +2071,26 @@
       <c r="A11" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="B11" s="26" t="s">
+      <c r="B11" s="26">
+        <v>0.0</v>
+      </c>
+      <c r="C11" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="C11" s="26" t="s">
+      <c r="D11" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="D11" s="26" t="s">
+      <c r="E11" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="E11" s="26" t="s">
+      <c r="F11" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="G11" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="H11" s="26" t="s">
         <v>98</v>
-      </c>
-      <c r="F11" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="G11" s="26" t="s">
-        <v>98</v>
-      </c>
-      <c r="H11" s="26" t="s">
-        <v>90</v>
       </c>
       <c r="I11" s="26" t="s">
         <v>99</v>
@@ -2102,24 +2119,24 @@
         <v>81</v>
       </c>
       <c r="H12" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="I12" s="26" t="s">
         <v>103</v>
-      </c>
-      <c r="I12" s="26" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="26" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B13" s="26">
         <v>0.0</v>
       </c>
       <c r="C13" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="D13" s="26" t="s">
         <v>106</v>
-      </c>
-      <c r="D13" s="26" t="s">
-        <v>107</v>
       </c>
       <c r="E13" s="26" t="s">
         <v>88</v>
@@ -2131,10 +2148,10 @@
         <v>88</v>
       </c>
       <c r="H13" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="I13" s="26" t="s">
         <v>103</v>
-      </c>
-      <c r="I13" s="26" t="s">
-        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -2187,16 +2204,16 @@
     </row>
     <row r="2">
       <c r="A2" s="28" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B2" s="28" t="s">
         <v>64</v>
       </c>
       <c r="C2" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="D2" s="28" t="s">
         <v>109</v>
-      </c>
-      <c r="D2" s="28" t="s">
-        <v>110</v>
       </c>
       <c r="E2" s="28" t="s">
         <v>52</v>
@@ -2211,21 +2228,21 @@
         <v>53</v>
       </c>
       <c r="I2" s="28" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="B3" s="28" t="s">
         <v>112</v>
       </c>
-      <c r="B3" s="28" t="s">
+      <c r="C3" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="D3" s="28" t="s">
         <v>113</v>
-      </c>
-      <c r="C3" s="28" t="s">
-        <v>109</v>
-      </c>
-      <c r="D3" s="28" t="s">
-        <v>114</v>
       </c>
       <c r="E3" s="28" t="s">
         <v>52</v>
@@ -2240,21 +2257,21 @@
         <v>83</v>
       </c>
       <c r="I3" s="28" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" s="28">
+        <v>30.0</v>
+      </c>
+      <c r="C4" s="28" t="s">
         <v>116</v>
       </c>
-      <c r="B4" s="28">
-        <v>20.0</v>
-      </c>
-      <c r="C4" s="28" t="s">
+      <c r="D4" s="28" t="s">
         <v>117</v>
-      </c>
-      <c r="D4" s="28" t="s">
-        <v>118</v>
       </c>
       <c r="E4" s="28" t="s">
         <v>73</v>
@@ -2263,172 +2280,172 @@
         <v>45</v>
       </c>
       <c r="G4" s="28" t="s">
-        <v>119</v>
+        <v>67</v>
       </c>
       <c r="H4" s="28" t="s">
         <v>75</v>
       </c>
       <c r="I4" s="28" t="s">
-        <v>115</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="B5" s="28">
+        <v>20.0</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="D5" s="28" t="s">
         <v>120</v>
       </c>
-      <c r="B5" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="C5" s="28" t="s">
-        <v>121</v>
-      </c>
-      <c r="D5" s="28" t="s">
-        <v>122</v>
-      </c>
       <c r="E5" s="28" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="F5" s="28" t="s">
         <v>45</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>73</v>
+        <v>121</v>
       </c>
       <c r="H5" s="28" t="s">
         <v>75</v>
       </c>
       <c r="I5" s="28" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" s="28" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="6" ht="28.5" customHeight="1">
-      <c r="A6" s="28" t="s">
+      <c r="D6" s="28" t="s">
         <v>124</v>
       </c>
-      <c r="B6" s="28">
+      <c r="E6" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="G6" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="H6" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="I6" s="28" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="7" ht="28.5" customHeight="1">
+      <c r="A7" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="B7" s="28">
         <v>0.0</v>
       </c>
-      <c r="C6" s="28" t="s">
-        <v>125</v>
-      </c>
-      <c r="D6" s="28" t="s">
-        <v>126</v>
-      </c>
-      <c r="E6" s="28" t="s">
+      <c r="C7" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="D7" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="E7" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="F6" s="28" t="s">
+      <c r="F7" s="28" t="s">
         <v>88</v>
       </c>
-      <c r="G6" s="28" t="s">
+      <c r="G7" s="28" t="s">
         <v>81</v>
-      </c>
-      <c r="H6" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="I6" s="28" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="28" t="s">
-        <v>127</v>
-      </c>
-      <c r="B7" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="C7" s="28" t="s">
-        <v>109</v>
-      </c>
-      <c r="D7" s="28" t="s">
-        <v>129</v>
-      </c>
-      <c r="E7" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="F7" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="G7" s="28" t="s">
-        <v>89</v>
       </c>
       <c r="H7" s="28" t="s">
         <v>90</v>
       </c>
       <c r="I7" s="28" t="s">
-        <v>130</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="D8" s="28" t="s">
         <v>131</v>
       </c>
-      <c r="B8" s="28">
-        <v>0.0</v>
-      </c>
-      <c r="C8" s="28" t="s">
-        <v>132</v>
-      </c>
-      <c r="D8" s="28" t="s">
-        <v>133</v>
-      </c>
       <c r="E8" s="28" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="F8" s="28" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="G8" s="28" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="H8" s="28" t="s">
         <v>90</v>
       </c>
       <c r="I8" s="28" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="28" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B9" s="28">
         <v>0.0</v>
       </c>
       <c r="C9" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="D9" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="E9" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="F9" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="G9" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="H9" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="I9" s="28" t="s">
         <v>136</v>
-      </c>
-      <c r="D9" s="28" t="s">
-        <v>137</v>
-      </c>
-      <c r="E9" s="28" t="s">
-        <v>88</v>
-      </c>
-      <c r="F9" s="28" t="s">
-        <v>88</v>
-      </c>
-      <c r="G9" s="28" t="s">
-        <v>81</v>
-      </c>
-      <c r="H9" s="28" t="s">
-        <v>103</v>
-      </c>
-      <c r="I9" s="28" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="28" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B10" s="28">
         <v>0.0</v>
       </c>
       <c r="C10" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="D10" s="28" t="s">
         <v>139</v>
-      </c>
-      <c r="D10" s="28" t="s">
-        <v>140</v>
       </c>
       <c r="E10" s="28" t="s">
         <v>88</v>
@@ -2437,27 +2454,27 @@
         <v>88</v>
       </c>
       <c r="G10" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="H10" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="H10" s="28" t="s">
-        <v>103</v>
-      </c>
       <c r="I10" s="28" t="s">
-        <v>141</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="28" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B11" s="28">
         <v>0.0</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E11" s="28" t="s">
         <v>88</v>
@@ -2466,24 +2483,24 @@
         <v>88</v>
       </c>
       <c r="G11" s="28" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="H11" s="28" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="I11" s="28" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="28" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B12" s="28">
         <v>0.0</v>
       </c>
       <c r="C12" s="28" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="D12" s="28" t="s">
         <v>146</v>
@@ -2498,10 +2515,39 @@
         <v>88</v>
       </c>
       <c r="H12" s="28" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="I12" s="28" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="B13" s="28">
+        <v>0.0</v>
+      </c>
+      <c r="C13" s="28" t="s">
         <v>141</v>
+      </c>
+      <c r="D13" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="E13" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="F13" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="G13" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="H13" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="I13" s="28" t="s">
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -2554,16 +2600,16 @@
     </row>
     <row r="2">
       <c r="A2" s="30" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B2" s="30" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C2" s="30" t="s">
         <v>60</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E2" s="30" t="s">
         <v>45</v>
@@ -2583,16 +2629,16 @@
     </row>
     <row r="3">
       <c r="A3" s="30" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B3" s="30" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C3" s="30" t="s">
         <v>60</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E3" s="30" t="s">
         <v>73</v>
@@ -2601,7 +2647,7 @@
         <v>45</v>
       </c>
       <c r="G3" s="30" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H3" s="30" t="s">
         <v>46</v>
@@ -2612,16 +2658,16 @@
     </row>
     <row r="4">
       <c r="A4" s="30" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B4" s="30" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C4" s="30" t="s">
         <v>60</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E4" s="30" t="s">
         <v>45</v>
@@ -2636,21 +2682,21 @@
         <v>46</v>
       </c>
       <c r="I4" s="30" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="30" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C5" s="30" t="s">
         <v>60</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E5" s="30" t="s">
         <v>73</v>
@@ -2670,16 +2716,16 @@
     </row>
     <row r="6">
       <c r="A6" s="30" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B6" s="30">
         <v>20.0</v>
       </c>
       <c r="C6" s="30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E6" s="30" t="s">
         <v>89</v>
@@ -2699,16 +2745,16 @@
     </row>
     <row r="7">
       <c r="A7" s="30" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B7" s="30">
         <v>10.0</v>
       </c>
       <c r="C7" s="30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E7" s="30" t="s">
         <v>89</v>
@@ -2723,21 +2769,21 @@
         <v>83</v>
       </c>
       <c r="I7" s="30" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="30" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B8" s="30" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C8" s="30" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D8" s="30" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E8" s="30" t="s">
         <v>73</v>
@@ -2749,7 +2795,7 @@
         <v>67</v>
       </c>
       <c r="H8" s="30" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I8" s="30" t="s">
         <v>47</v>
@@ -2757,16 +2803,16 @@
     </row>
     <row r="9">
       <c r="A9" s="30" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B9" s="30">
         <v>0.0</v>
       </c>
       <c r="C9" s="30" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E9" s="30" t="s">
         <v>88</v>
@@ -2775,59 +2821,59 @@
         <v>88</v>
       </c>
       <c r="G9" s="30" t="s">
+        <v>97</v>
+      </c>
+      <c r="H9" s="30" t="s">
         <v>98</v>
       </c>
-      <c r="H9" s="30" t="s">
-        <v>103</v>
-      </c>
       <c r="I9" s="30" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="30" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B10" s="30" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C10" s="30" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E10" s="30" t="s">
         <v>88</v>
       </c>
       <c r="F10" s="30" t="s">
+        <v>97</v>
+      </c>
+      <c r="G10" s="30" t="s">
+        <v>97</v>
+      </c>
+      <c r="H10" s="30" t="s">
         <v>98</v>
       </c>
-      <c r="G10" s="30" t="s">
-        <v>98</v>
-      </c>
-      <c r="H10" s="30" t="s">
-        <v>103</v>
-      </c>
       <c r="I10" s="30" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="30" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B11" s="30" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C11" s="30" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D11" s="30" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E11" s="30" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F11" s="30" t="s">
         <v>67</v>
@@ -2836,24 +2882,24 @@
         <v>67</v>
       </c>
       <c r="H11" s="30" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="I11" s="30" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="30" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B12" s="30">
         <v>0.0</v>
       </c>
       <c r="C12" s="30" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D12" s="30" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E12" s="30" t="s">
         <v>88</v>
@@ -2865,10 +2911,10 @@
         <v>88</v>
       </c>
       <c r="H12" s="30" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="I12" s="30" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -2921,16 +2967,16 @@
     </row>
     <row r="2">
       <c r="A2" s="32" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B2" s="32" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C2" s="32" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D2" s="32" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E2" s="32" t="s">
         <v>45</v>
@@ -2945,21 +2991,21 @@
         <v>46</v>
       </c>
       <c r="I2" s="32" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="32" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B3" s="32" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C3" s="32" t="s">
         <v>60</v>
       </c>
       <c r="D3" s="32" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E3" s="32" t="s">
         <v>45</v>
@@ -2974,21 +3020,21 @@
         <v>46</v>
       </c>
       <c r="I3" s="32" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="32" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B4" s="32" t="s">
         <v>64</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>198</v>
+        <v>116</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E4" s="32" t="s">
         <v>45</v>
@@ -3003,21 +3049,21 @@
         <v>68</v>
       </c>
       <c r="I4" s="32" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="32" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C5" s="32" t="s">
         <v>101</v>
       </c>
       <c r="D5" s="32" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E5" s="32" t="s">
         <v>89</v>
@@ -3037,16 +3083,16 @@
     </row>
     <row r="6">
       <c r="A6" s="32" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C6" s="32" t="s">
         <v>60</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E6" s="32" t="s">
         <v>73</v>
@@ -3066,16 +3112,16 @@
     </row>
     <row r="7">
       <c r="A7" s="32" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B7" s="32" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C7" s="32" t="s">
         <v>60</v>
       </c>
       <c r="D7" s="32" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E7" s="32" t="s">
         <v>45</v>
@@ -3095,16 +3141,16 @@
     </row>
     <row r="8">
       <c r="A8" s="32" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B8" s="32">
         <v>1.0</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D8" s="32" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E8" s="32" t="s">
         <v>89</v>
@@ -3119,24 +3165,24 @@
         <v>83</v>
       </c>
       <c r="I8" s="32" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="32" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B9" s="32" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D9" s="32" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F9" s="32" t="s">
         <v>73</v>
@@ -3148,21 +3194,21 @@
         <v>75</v>
       </c>
       <c r="I9" s="32" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="32" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B10" s="32">
         <v>0.0</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D10" s="32" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E10" s="32" t="s">
         <v>88</v>
@@ -3174,24 +3220,24 @@
         <v>89</v>
       </c>
       <c r="H10" s="32" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="I10" s="32" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="32" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B11" s="32">
         <v>0.0</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D11" s="32" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E11" s="32" t="s">
         <v>88</v>
@@ -3203,10 +3249,10 @@
         <v>88</v>
       </c>
       <c r="H11" s="32" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="I11" s="32" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
   </sheetData>
@@ -3262,16 +3308,16 @@
     </row>
     <row r="2">
       <c r="A2" s="35" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B2" s="35" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C2" s="35" t="s">
         <v>50</v>
       </c>
       <c r="D2" s="35" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E2" s="35" t="s">
         <v>52</v>
@@ -3291,16 +3337,16 @@
     </row>
     <row r="3">
       <c r="A3" s="35" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C3" s="35" t="s">
         <v>50</v>
       </c>
       <c r="D3" s="35" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E3" s="35" t="s">
         <v>52</v>
@@ -3320,7 +3366,7 @@
     </row>
     <row r="4">
       <c r="A4" s="35" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B4" s="35">
         <v>30.0</v>
@@ -3329,7 +3375,7 @@
         <v>50</v>
       </c>
       <c r="D4" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E4" s="35" t="s">
         <v>52</v>
@@ -3344,21 +3390,21 @@
         <v>53</v>
       </c>
       <c r="I4" s="35" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="35" t="s">
-        <v>230</v>
-      </c>
-      <c r="B5" s="35">
-        <v>30.0</v>
+        <v>231</v>
+      </c>
+      <c r="B5" s="35" t="s">
+        <v>85</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D5" s="35" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E5" s="35" t="s">
         <v>52</v>
@@ -3373,21 +3419,21 @@
         <v>53</v>
       </c>
       <c r="I5" s="35" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B6" s="35">
         <v>30.0</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>50</v>
+        <v>236</v>
       </c>
       <c r="D6" s="35" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E6" s="35" t="s">
         <v>52</v>
@@ -3399,15 +3445,15 @@
         <v>52</v>
       </c>
       <c r="H6" s="35" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="I6" s="35" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B7" s="35">
         <v>30.0</v>
@@ -3416,10 +3462,10 @@
         <v>50</v>
       </c>
       <c r="D7" s="35" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E7" s="35" t="s">
-        <v>239</v>
+        <v>52</v>
       </c>
       <c r="F7" s="35" t="s">
         <v>52</v>
@@ -3431,27 +3477,27 @@
         <v>83</v>
       </c>
       <c r="I7" s="35" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="s">
-        <v>241</v>
-      </c>
-      <c r="B8" s="35" t="s">
         <v>242</v>
       </c>
+      <c r="B8" s="35">
+        <v>30.0</v>
+      </c>
       <c r="C8" s="35" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="35" t="s">
         <v>243</v>
       </c>
-      <c r="D8" s="35" t="s">
+      <c r="E8" s="35" t="s">
         <v>244</v>
       </c>
-      <c r="E8" s="35" t="s">
-        <v>89</v>
-      </c>
       <c r="F8" s="35" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="G8" s="35" t="s">
         <v>52</v>
@@ -3460,7 +3506,36 @@
         <v>83</v>
       </c>
       <c r="I8" s="35" t="s">
-        <v>240</v>
+        <v>245</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="35" t="s">
+        <v>246</v>
+      </c>
+      <c r="B9" s="35" t="s">
+        <v>247</v>
+      </c>
+      <c r="C9" s="35" t="s">
+        <v>248</v>
+      </c>
+      <c r="D9" s="35" t="s">
+        <v>249</v>
+      </c>
+      <c r="E9" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="F9" s="35" t="s">
+        <v>81</v>
+      </c>
+      <c r="G9" s="35" t="s">
+        <v>52</v>
+      </c>
+      <c r="H9" s="35" t="s">
+        <v>83</v>
+      </c>
+      <c r="I9" s="35" t="s">
+        <v>245</v>
       </c>
     </row>
   </sheetData>
